--- a/public/sample/거래명세서_동방정공_2026하반기.xlsx
+++ b/public/sample/거래명세서_동방정공_2026하반기.xlsx
@@ -37,7 +37,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>납품 후 30일</t>
+          <t>납품 후 45일</t>
         </is>
       </c>
     </row>
@@ -60,6 +60,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>공급가액</t>
         </is>
       </c>
@@ -67,79 +72,499 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>알루미늄 브라켓</t>
+          <t>샤프트 어셈블리</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12,300,000</t>
+          <t>127,100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,900,000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>알루미늄 브라켓</t>
+          <t>기어 블랭크</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14,800,000</t>
+          <t>122,800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9,950,000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>알루미늄 브라켓</t>
+          <t>기어 블랭크</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17,500,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>142,500</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10,400,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>플랜지</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>120,200</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10,100,000</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>부싱</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>103,200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9,800,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>플랜지</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>156,600</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>11,900,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>부싱</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>133,300</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>11,600,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>샤프트 어셈블리</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>115,300</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>11,300,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>기어 블랭크</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>100,900</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>11,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>부싱</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>152,500</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>12,050,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>샤프트 어셈블리</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>130,600</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11,750,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>샤프트 어셈블리</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>165,200</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>13,550,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>기어 블랭크</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>142,500</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>13,250,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>플랜지</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>124,500</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>12,950,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>기어 블랭크</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>161,200</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>13,700,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-12-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>플랜지</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>139,600</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>13,400,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>부싱</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>135,000</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>14,450,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>샤프트 어셈블리</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>181,400</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>14,150,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>합계금액</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>44,600,000</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>214,200,000</t>
         </is>
       </c>
     </row>

--- a/public/sample/거래명세서_동방정공_2026하반기.xlsx
+++ b/public/sample/거래명세서_동방정공_2026하반기.xlsx
@@ -99,7 +99,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -126,7 +126,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -153,7 +153,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -180,7 +180,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -207,7 +207,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -234,7 +234,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -261,7 +261,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -288,7 +288,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -315,7 +315,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -342,7 +342,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -396,7 +396,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -423,7 +423,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -450,7 +450,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -477,7 +477,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -531,7 +531,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
